--- a/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
+++ b/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
@@ -67948,7 +67948,7 @@
       </c>
       <c r="G1057" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H1057" s="5" t="n">
@@ -91774,7 +91774,7 @@
           <t>B | 628呎 (3房)
 $1247万
 $19,861/呎
-(26年-08月-03日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">

--- a/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
+++ b/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
@@ -35720,7 +35720,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="G612" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H612" s="5" t="n">
@@ -86776,7 +86776,7 @@
           <t>C | 584呎 (2房)
 $1065万
 $18,233/呎
-(26年-08月-05日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="E45" s="22" t="inlineStr">
@@ -87336,7 +87336,7 @@
           <t>A | 612呎 (2房)
 $1177万
 $19,230/呎
-(26年-08月-14日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">

--- a/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
+++ b/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
@@ -18720,7 +18720,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -34790,7 +34790,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -84272,7 +84272,7 @@
           <t>B | 455呎 (2房)
 $918万
 $20,168/呎
-(26年-08月-10日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -86656,7 +86656,7 @@
           <t>D | 463呎 (2房)
 $807万
 $17,431/呎
-(26年-08月-15日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="F43" s="22" t="inlineStr">

--- a/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
+++ b/九龙-将军澳-海瑅湾 I/海瑅湾 I_销控明细表.xlsx
@@ -24965,38 +24965,30 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H374" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I374" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H374" s="5" t="n">
+        <v>12861000</v>
+      </c>
+      <c r="I374" s="5" t="n">
+        <v>20912</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K374" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L374" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K374" s="5" t="n">
+        <v>12861000</v>
+      </c>
+      <c r="L374" s="5" t="n">
+        <v>20912</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
@@ -25005,7 +24997,7 @@
       </c>
       <c r="N374" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38758,7 +38750,7 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H596" s="5" t="n">
@@ -41324,7 +41316,7 @@
       </c>
       <c r="G637" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H637" s="5" t="n">
@@ -84125,7 +84117,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -84135,7 +84127,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -85155,12 +85147,12 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 615呎 (2房)
-招标单位
--
-(在售)</t>
+$1286万
+$20,912/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -87224,7 +87216,7 @@
           <t>C | 584呎 (2房)
 $1024万
 $17,531/呎
-(26年-08月-14日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
@@ -87616,7 +87608,7 @@
           <t>D | 463呎 (2房)
 $783万
 $16,917/呎
-(26年-08月-16日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="F58" s="22" t="inlineStr">
